--- a/data/raw/female_life_table_south_brazil_2025.xlsx
+++ b/data/raw/female_life_table_south_brazil_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/Projeto IC - Vanessa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6671f81417a0f489/Documentos/projeto_longevidade/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC41D23-0D4C-4465-B1A3-00F0AB0CCABE}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_F25DC773A252ABDACC104828F1DA7B125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67845B4C-44AF-4494-AE50-9D981F7AC489}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1056" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -516,31 +516,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>8.7341452016619896E-3</v>
+        <v>9.0144403295725293E-3</v>
       </c>
       <c r="C2" s="4">
-        <v>7.5992664039000304E-2</v>
+        <v>7.6820125250226495E-2</v>
       </c>
       <c r="D2" s="4">
-        <v>8.6642213463327695E-3</v>
+        <v>8.9400417500746197E-3</v>
       </c>
       <c r="E2" s="5">
         <v>100000</v>
       </c>
       <c r="F2" s="5">
-        <v>866.42213463327801</v>
+        <v>894.00417500746005</v>
       </c>
       <c r="G2" s="5">
-        <v>99199.419591559898</v>
+        <v>99174.673337690794</v>
       </c>
       <c r="H2" s="6">
-        <v>0.990759976019017</v>
+        <v>0.99047147452363504</v>
       </c>
       <c r="I2" s="5">
-        <v>8063125.5377796199</v>
+        <v>8027480.4095491199</v>
       </c>
       <c r="J2" s="7">
-        <v>80.631255377796194</v>
+        <v>80.274804095491206</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -548,31 +548,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="4">
-        <v>3.5857280836242998E-4</v>
+        <v>3.6791908495401E-4</v>
       </c>
       <c r="C3" s="4">
-        <v>1.5098965805898199</v>
+        <v>1.5094475679796799</v>
       </c>
       <c r="D3" s="4">
-        <v>1.43301172110603E-3</v>
+        <v>1.4703290453000901E-3</v>
       </c>
       <c r="E3" s="5">
-        <v>99133.577865366693</v>
+        <v>99105.995824992497</v>
       </c>
       <c r="F3" s="5">
-        <v>142.05957903625699</v>
+        <v>145.71842422486199</v>
       </c>
       <c r="G3" s="5">
-        <v>396180.56841794902</v>
+        <v>396061.06392412703</v>
       </c>
       <c r="H3" s="6">
-        <v>0.99870263562636996</v>
+        <v>0.998664678636346</v>
       </c>
       <c r="I3" s="5">
-        <v>7963926.1181880599</v>
+        <v>7928305.7362114303</v>
       </c>
       <c r="J3" s="7">
-        <v>80.335304037990696</v>
+        <v>79.998245012458298</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -580,31 +580,31 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>1.6854882602659199E-4</v>
+        <v>1.7389546051966399E-4</v>
       </c>
       <c r="C4" s="4">
-        <v>2.3582124680498202</v>
+        <v>2.3611931648556399</v>
       </c>
       <c r="D4" s="4">
-        <v>8.42369048309191E-4</v>
+        <v>8.6907850287078398E-4</v>
       </c>
       <c r="E4" s="5">
-        <v>98991.518286330494</v>
+        <v>98960.277400767707</v>
       </c>
       <c r="F4" s="5">
-        <v>83.387391049516694</v>
+        <v>86.004249727135203</v>
       </c>
       <c r="G4" s="5">
-        <v>494737.29966165603</v>
+        <v>494574.43840180698</v>
       </c>
       <c r="H4" s="6">
-        <v>0.99916319496921902</v>
+        <v>0.99913293840102302</v>
       </c>
       <c r="I4" s="5">
-        <v>7567745.5497701103</v>
+        <v>7532244.6722873002</v>
       </c>
       <c r="J4" s="7">
-        <v>76.4484238728473</v>
+        <v>76.113819303308304</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -612,31 +612,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="4">
-        <v>1.88139140709473E-4</v>
+        <v>1.9569471624266099E-4</v>
       </c>
       <c r="C5" s="4">
-        <v>2.6629050793327398</v>
+        <v>2.6654609889960699</v>
       </c>
       <c r="D5" s="4">
-        <v>9.4028226234855897E-4</v>
+        <v>9.7802676289006395E-4</v>
       </c>
       <c r="E5" s="5">
-        <v>98908.130895280905</v>
+        <v>98874.273151040499</v>
       </c>
       <c r="F5" s="5">
-        <v>93.001561082885004</v>
+        <v>96.701685303036399</v>
       </c>
       <c r="G5" s="5">
-        <v>494323.30100038397</v>
+        <v>494145.61189843301</v>
       </c>
       <c r="H5" s="6">
-        <v>0.99864981429067201</v>
+        <v>0.99859154075549506</v>
       </c>
       <c r="I5" s="5">
-        <v>7073008.2501084497</v>
+        <v>7037670.2338854903</v>
       </c>
       <c r="J5" s="7">
-        <v>71.510887791388996</v>
+        <v>71.177971878839799</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -644,31 +644,31 @@
         <v>15</v>
       </c>
       <c r="B6" s="4">
-        <v>3.6909396108975999E-4</v>
+        <v>3.8553192781142301E-4</v>
       </c>
       <c r="C6" s="4">
-        <v>2.6961499276027099</v>
+        <v>2.6964464108414399</v>
       </c>
       <c r="D6" s="4">
-        <v>1.8439018671920599E-3</v>
+        <v>1.9259492161615699E-3</v>
       </c>
       <c r="E6" s="5">
-        <v>98815.129334198107</v>
+        <v>98777.571465737507</v>
       </c>
       <c r="F6" s="5">
-        <v>182.20540148616399</v>
+        <v>190.240586338768</v>
       </c>
       <c r="G6" s="5">
-        <v>493655.87274358497</v>
+        <v>493449.62794322299</v>
       </c>
       <c r="H6" s="6">
-        <v>0.99784963840696705</v>
+        <v>0.99775687583831896</v>
       </c>
       <c r="I6" s="5">
-        <v>6578684.9491080698</v>
+        <v>6543524.6219870597</v>
       </c>
       <c r="J6" s="7">
-        <v>66.575685256238501</v>
+        <v>66.245044546947398</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -676,31 +676,31 @@
         <v>20</v>
       </c>
       <c r="B7" s="4">
-        <v>4.8414884544238998E-4</v>
+        <v>5.0439211225083199E-4</v>
       </c>
       <c r="C7" s="4">
-        <v>2.6087551158056499</v>
+        <v>2.6084800915857</v>
       </c>
       <c r="D7" s="4">
-        <v>2.4179449277583601E-3</v>
+        <v>2.51892207679308E-3</v>
       </c>
       <c r="E7" s="5">
-        <v>98632.923932711899</v>
+        <v>98587.330879398694</v>
       </c>
       <c r="F7" s="5">
-        <v>238.48897813307099</v>
+        <v>248.33380424421901</v>
       </c>
       <c r="G7" s="5">
-        <v>492594.33411466202</v>
+        <v>492342.75916021102</v>
       </c>
       <c r="H7" s="6">
-        <v>0.99724728804864604</v>
+        <v>0.99713056794230503</v>
       </c>
       <c r="I7" s="5">
-        <v>6085029.0763644902</v>
+        <v>6050074.9940438401</v>
       </c>
       <c r="J7" s="7">
-        <v>61.693690440686296</v>
+        <v>61.367672094144197</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -708,31 +708,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="4">
-        <v>6.2510353564398805E-4</v>
+        <v>6.5221376728640998E-4</v>
       </c>
       <c r="C8" s="4">
-        <v>2.6103187953798801</v>
+        <v>2.6108961199390701</v>
       </c>
       <c r="D8" s="4">
-        <v>3.1208557496121198E-3</v>
+        <v>3.2559953235436101E-3</v>
       </c>
       <c r="E8" s="5">
-        <v>98394.434954578799</v>
+        <v>98338.997075154504</v>
       </c>
       <c r="F8" s="5">
-        <v>307.07483805782999</v>
+        <v>320.191314598676</v>
       </c>
       <c r="G8" s="5">
-        <v>491238.36380397598</v>
+        <v>490930.015063703</v>
       </c>
       <c r="H8" s="6">
-        <v>0.99640350048007797</v>
+        <v>0.99624470453958403</v>
       </c>
       <c r="I8" s="5">
-        <v>5592434.7422498204</v>
+        <v>5557732.2348836297</v>
       </c>
       <c r="J8" s="7">
-        <v>56.836900835209001</v>
+        <v>56.516055686801302</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -740,31 +740,31 @@
         <v>30</v>
       </c>
       <c r="B9" s="4">
-        <v>8.2730517753086595E-4</v>
+        <v>8.6452262801357501E-4</v>
       </c>
       <c r="C9" s="4">
-        <v>2.6165121390736101</v>
+        <v>2.6169859008080301</v>
       </c>
       <c r="D9" s="4">
-        <v>4.12838524102017E-3</v>
+        <v>4.3137261325766601E-3</v>
       </c>
       <c r="E9" s="5">
-        <v>98087.360116520998</v>
+        <v>98018.805760555799</v>
       </c>
       <c r="F9" s="5">
-        <v>404.94240983568301</v>
+        <v>422.82628389325703</v>
       </c>
       <c r="G9" s="5">
-        <v>489471.625264387</v>
+        <v>489086.42780675302</v>
       </c>
       <c r="H9" s="6">
-        <v>0.99525693551589001</v>
+        <v>0.99504085570925205</v>
       </c>
       <c r="I9" s="5">
-        <v>5101196.3784458498</v>
+        <v>5066802.2198199201</v>
       </c>
       <c r="J9" s="7">
-        <v>52.006663981842102</v>
+        <v>51.692143976914998</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,31 +772,31 @@
         <v>35</v>
       </c>
       <c r="B10" s="4">
-        <v>1.1026245951127501E-3</v>
+        <v>1.1534928998511501E-3</v>
       </c>
       <c r="C10" s="4">
-        <v>2.6504258068161</v>
+        <v>2.6504920475530098</v>
       </c>
       <c r="D10" s="4">
-        <v>5.4988770441894898E-3</v>
+        <v>5.7518761054834002E-3</v>
       </c>
       <c r="E10" s="5">
-        <v>97682.417706685301</v>
+        <v>97595.9794766626</v>
       </c>
       <c r="F10" s="5">
-        <v>537.14360434822402</v>
+        <v>561.35998234306999</v>
       </c>
       <c r="G10" s="5">
-        <v>487150.02978261601</v>
+        <v>486660.97764061199</v>
       </c>
       <c r="H10" s="6">
-        <v>0.99306280636871402</v>
+        <v>0.99274383437262703</v>
       </c>
       <c r="I10" s="5">
-        <v>4611724.7531814603</v>
+        <v>4577715.7920131702</v>
       </c>
       <c r="J10" s="7">
-        <v>47.211410829626097</v>
+        <v>46.904757927121402</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -804,31 +804,31 @@
         <v>40</v>
       </c>
       <c r="B11" s="4">
-        <v>1.7220035786723201E-3</v>
+        <v>1.8009583821460601E-3</v>
       </c>
       <c r="C11" s="4">
-        <v>2.6522611289009999</v>
+        <v>2.6515103866630398</v>
       </c>
       <c r="D11" s="4">
-        <v>8.57534934464909E-3</v>
+        <v>8.9668662624446706E-3</v>
       </c>
       <c r="E11" s="5">
-        <v>97145.274102337105</v>
+        <v>97034.619494319501</v>
       </c>
       <c r="F11" s="5">
-        <v>833.05466260922503</v>
+        <v>870.09645583276904</v>
       </c>
       <c r="G11" s="5">
-        <v>483770.57569852797</v>
+        <v>483129.68498247297</v>
       </c>
       <c r="H11" s="6">
-        <v>0.99000603243671403</v>
+        <v>0.98956449657496903</v>
       </c>
       <c r="I11" s="5">
-        <v>4124574.7233988401</v>
+        <v>4091054.81437256</v>
       </c>
       <c r="J11" s="7">
-        <v>42.457801076909199</v>
+        <v>42.160775563324101</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -836,31 +836,31 @@
         <v>45</v>
       </c>
       <c r="B12" s="4">
-        <v>2.3297635643602199E-3</v>
+        <v>2.4303956987997101E-3</v>
       </c>
       <c r="C12" s="4">
-        <v>2.6471660504082402</v>
+        <v>2.6465009537044701</v>
       </c>
       <c r="D12" s="4">
-        <v>1.1585312389643301E-2</v>
+        <v>1.2082865302430201E-2</v>
       </c>
       <c r="E12" s="5">
-        <v>96312.219439727894</v>
+        <v>96164.523038486703</v>
       </c>
       <c r="F12" s="5">
-        <v>1115.8071491491301</v>
+        <v>1161.9429787464801</v>
       </c>
       <c r="G12" s="5">
-        <v>478935.78825692402</v>
+        <v>478087.98350010399</v>
       </c>
       <c r="H12" s="6">
-        <v>0.98559478090712005</v>
+        <v>0.984974054520669</v>
       </c>
       <c r="I12" s="5">
-        <v>3640804.14770032</v>
+        <v>3607925.12939008</v>
       </c>
       <c r="J12" s="7">
-        <v>37.802099971112497</v>
+        <v>37.518255333582097</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -868,31 +868,31 @@
         <v>50</v>
       </c>
       <c r="B13" s="4">
-        <v>3.57220539161558E-3</v>
+        <v>3.72783446437347E-3</v>
       </c>
       <c r="C13" s="4">
-        <v>2.6601703835825998</v>
+        <v>2.6594984467135601</v>
       </c>
       <c r="D13" s="4">
-        <v>1.7712975672945601E-2</v>
+        <v>1.8477952145892498E-2</v>
       </c>
       <c r="E13" s="5">
-        <v>95196.412290578694</v>
+        <v>95002.580059740299</v>
       </c>
       <c r="F13" s="5">
-        <v>1686.2117350547201</v>
+        <v>1755.4531280802</v>
       </c>
       <c r="G13" s="5">
-        <v>472036.61329566198</v>
+        <v>470904.25952570798</v>
       </c>
       <c r="H13" s="6">
-        <v>0.97852479817452498</v>
+        <v>0.97762323034087795</v>
       </c>
       <c r="I13" s="5">
-        <v>3161868.3594433898</v>
+        <v>3129837.1458899798</v>
       </c>
       <c r="J13" s="7">
-        <v>33.214154644736702</v>
+        <v>32.9447594362369</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -900,31 +900,31 @@
         <v>55</v>
       </c>
       <c r="B14" s="4">
-        <v>5.2085769643621296E-3</v>
+        <v>5.4244958920075899E-3</v>
       </c>
       <c r="C14" s="4">
-        <v>2.6509357407136598</v>
+        <v>2.6499465071263502</v>
       </c>
       <c r="D14" s="4">
-        <v>2.5728094332618499E-2</v>
+        <v>2.6781078145223899E-2</v>
       </c>
       <c r="E14" s="5">
-        <v>93510.200555524003</v>
+        <v>93247.126931660096</v>
       </c>
       <c r="F14" s="5">
-        <v>2405.8392609545999</v>
+        <v>2497.2585931744102</v>
       </c>
       <c r="G14" s="5">
-        <v>461899.53175612399</v>
+        <v>460366.94337880198</v>
       </c>
       <c r="H14" s="6">
-        <v>0.96863519792081099</v>
+        <v>0.96736213729009202</v>
       </c>
       <c r="I14" s="5">
-        <v>2689831.7461477299</v>
+        <v>2658932.88636427</v>
       </c>
       <c r="J14" s="7">
-        <v>28.7651157859572</v>
+        <v>28.514904146193999</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -932,31 +932,31 @@
         <v>60</v>
       </c>
       <c r="B15" s="4">
-        <v>7.76604081488838E-3</v>
+        <v>8.0834251355870104E-3</v>
       </c>
       <c r="C15" s="4">
-        <v>2.66602971346888</v>
+        <v>2.6644278310354301</v>
       </c>
       <c r="D15" s="4">
-        <v>3.81389093213488E-2</v>
+        <v>3.9668212719217402E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>91104.361294569404</v>
+        <v>90749.868338485699</v>
       </c>
       <c r="F15" s="5">
-        <v>3474.6209741929902</v>
+        <v>3599.8850814920202</v>
       </c>
       <c r="G15" s="5">
-        <v>447412.14436212298</v>
+        <v>445341.55028462497</v>
       </c>
       <c r="H15" s="6">
-        <v>0.95141796786991994</v>
+        <v>0.94957570564133298</v>
       </c>
       <c r="I15" s="5">
-        <v>2227932.2143916101</v>
+        <v>2198565.9429854699</v>
       </c>
       <c r="J15" s="7">
-        <v>24.4547262362994</v>
+        <v>24.226657109684101</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -964,31 +964,31 @@
         <v>65</v>
       </c>
       <c r="B16" s="4">
-        <v>1.2489767584243999E-2</v>
+        <v>1.29489255074126E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>2.6539963243714402</v>
+        <v>2.6507297887255699</v>
       </c>
       <c r="D16" s="4">
-        <v>6.06711112243256E-2</v>
+        <v>6.2833208353855793E-2</v>
       </c>
       <c r="E16" s="5">
-        <v>87629.740320376397</v>
+        <v>87149.983256993597</v>
       </c>
       <c r="F16" s="5">
-        <v>5316.5937215363201</v>
+        <v>5475.91305602173</v>
       </c>
       <c r="G16" s="5">
-        <v>425675.95318933402</v>
+        <v>422885.51686292799</v>
       </c>
       <c r="H16" s="6">
-        <v>0.92698689859927796</v>
+        <v>0.92468657792100595</v>
       </c>
       <c r="I16" s="5">
-        <v>1780520.0700294799</v>
+        <v>1753224.39270085</v>
       </c>
       <c r="J16" s="7">
-        <v>20.3186733581528</v>
+        <v>20.117323345098299</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -996,31 +996,31 @@
         <v>70</v>
       </c>
       <c r="B17" s="4">
-        <v>1.84274337648043E-2</v>
+        <v>1.8969035260425999E-2</v>
       </c>
       <c r="C17" s="4">
-        <v>2.6662376632422999</v>
+        <v>2.6631495998999899</v>
       </c>
       <c r="D17" s="4">
-        <v>8.8338163921978394E-2</v>
+        <v>9.0819354341290195E-2</v>
       </c>
       <c r="E17" s="5">
-        <v>82313.146598840103</v>
+        <v>81674.070200971895</v>
       </c>
       <c r="F17" s="5">
-        <v>7271.39223718217</v>
+        <v>7417.58632207746</v>
       </c>
       <c r="G17" s="5">
-        <v>394596.031655272</v>
+        <v>391036.56144033599</v>
       </c>
       <c r="H17" s="6">
-        <v>0.88252890236543202</v>
+        <v>0.87944838198305197</v>
       </c>
       <c r="I17" s="5">
-        <v>1354844.11684015</v>
+        <v>1330338.87583792</v>
       </c>
       <c r="J17" s="7">
-        <v>16.4596321829743</v>
+        <v>16.288387153528799</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,31 +1028,31 @@
         <v>75</v>
       </c>
       <c r="B18" s="4">
-        <v>3.3352236681638697E-2</v>
+        <v>3.4254613090997602E-2</v>
       </c>
       <c r="C18" s="4">
-        <v>2.6782478297197101</v>
+        <v>2.6752246322362101</v>
       </c>
       <c r="D18" s="4">
-        <v>0.15477600618547599</v>
+        <v>0.15863989177576501</v>
       </c>
       <c r="E18" s="5">
-        <v>75041.754361657906</v>
+        <v>74256.483878894403</v>
       </c>
       <c r="F18" s="5">
-        <v>11614.6630372489</v>
+        <v>11780.0405661967</v>
       </c>
       <c r="G18" s="5">
-        <v>348242.402694483</v>
+        <v>343896.47125492</v>
       </c>
       <c r="H18" s="6">
-        <v>0.79597300360219003</v>
+        <v>0.79142655597552203</v>
       </c>
       <c r="I18" s="5">
-        <v>960248.08518487797</v>
+        <v>939302.31439758104</v>
       </c>
       <c r="J18" s="7">
-        <v>12.7961838492879</v>
+        <v>12.649431609628801</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -1060,31 +1060,31 @@
         <v>80</v>
       </c>
       <c r="B19" s="4">
-        <v>6.0518703691147299E-2</v>
+        <v>6.1956485522940002E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>2.6188819985301799</v>
+        <v>2.6152335045416999</v>
       </c>
       <c r="D19" s="4">
-        <v>0.264481202050598</v>
+        <v>0.26990368551813498</v>
       </c>
       <c r="E19" s="5">
-        <v>63427.091324408997</v>
+        <v>62476.443312697797</v>
       </c>
       <c r="F19" s="5">
-        <v>16775.273356052701</v>
+        <v>16862.622308162001</v>
       </c>
       <c r="G19" s="5">
-        <v>277191.55125437101</v>
+        <v>272168.79985741602</v>
       </c>
       <c r="H19" s="6">
-        <v>0.66241920926907005</v>
+        <v>0.65581175758185095</v>
       </c>
       <c r="I19" s="5">
-        <v>612005.68249039503</v>
+        <v>595405.84314266103</v>
       </c>
       <c r="J19" s="7">
-        <v>9.6489633957859393</v>
+        <v>9.5300854461676803</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1092,31 +1092,31 @@
         <v>85</v>
       </c>
       <c r="B20" s="4">
-        <v>0.108087973705127</v>
+        <v>0.11066492270742</v>
       </c>
       <c r="C20" s="4">
-        <v>2.4987350217062398</v>
+        <v>2.4900906861294501</v>
       </c>
       <c r="D20" s="4">
-        <v>0.42542372876830198</v>
+        <v>0.433043044959462</v>
       </c>
       <c r="E20" s="5">
-        <v>46651.817968356299</v>
+        <v>45613.821004535799</v>
       </c>
       <c r="F20" s="5">
-        <v>19846.790353918201</v>
+        <v>19752.747940040099</v>
       </c>
       <c r="G20" s="5">
-        <v>183617.00819798699</v>
+        <v>178491.498993435</v>
       </c>
       <c r="H20" s="6">
-        <v>0.45158524964244001</v>
+        <v>0.44779998858013698</v>
       </c>
       <c r="I20" s="5">
-        <v>334814.13123602403</v>
+        <v>323237.04328524502</v>
       </c>
       <c r="J20" s="7">
-        <v>7.1768721095312298</v>
+        <v>7.0863838232956304</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1124,31 +1124,31 @@
         <v>90</v>
       </c>
       <c r="B21" s="4">
-        <v>0.17728530196764899</v>
+        <v>0.17866576267355999</v>
       </c>
       <c r="C21" s="4">
-        <v>5.6406255278989796</v>
+        <v>5.59704324452525</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
       <c r="E21" s="5">
-        <v>26805.027614438099</v>
+        <v>25861.0730644957</v>
       </c>
       <c r="F21" s="5">
-        <v>26805.027614438099</v>
+        <v>25861.0730644957</v>
       </c>
       <c r="G21" s="5">
-        <v>151197.12303803701</v>
+        <v>144745.54429180999</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
       </c>
       <c r="I21" s="5">
-        <v>151197.12303803701</v>
+        <v>144745.54429180999</v>
       </c>
       <c r="J21" s="7">
-        <v>5.6406255278989796</v>
+        <v>5.59704324452525</v>
       </c>
     </row>
   </sheetData>
